--- a/artfynd/A 22261-2024 artfynd.xlsx
+++ b/artfynd/A 22261-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136835174</v>
       </c>
       <c r="B2" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136835187</v>
       </c>
       <c r="B3" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136835198</v>
       </c>
       <c r="B4" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136835111</v>
       </c>
       <c r="B5" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22261-2024 artfynd.xlsx
+++ b/artfynd/A 22261-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136835174</v>
       </c>
       <c r="B2" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136835187</v>
       </c>
       <c r="B3" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136835198</v>
       </c>
       <c r="B4" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136835111</v>
       </c>
       <c r="B5" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22261-2024 artfynd.xlsx
+++ b/artfynd/A 22261-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136835174</v>
       </c>
       <c r="B2" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136835187</v>
       </c>
       <c r="B3" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136835198</v>
       </c>
       <c r="B4" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136835111</v>
       </c>
       <c r="B5" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22261-2024 artfynd.xlsx
+++ b/artfynd/A 22261-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136835174</v>
       </c>
       <c r="B2" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136835187</v>
       </c>
       <c r="B3" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136835198</v>
       </c>
       <c r="B4" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136835111</v>
       </c>
       <c r="B5" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22261-2024 artfynd.xlsx
+++ b/artfynd/A 22261-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136835174</v>
       </c>
       <c r="B2" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136835187</v>
       </c>
       <c r="B3" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136835198</v>
       </c>
       <c r="B4" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136835111</v>
       </c>
       <c r="B5" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22261-2024 artfynd.xlsx
+++ b/artfynd/A 22261-2024 artfynd.xlsx
@@ -1001,7 +1001,7 @@
         <v>136835111</v>
       </c>
       <c r="B5" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22261-2024 artfynd.xlsx
+++ b/artfynd/A 22261-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136835174</v>
       </c>
       <c r="B2" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136835187</v>
       </c>
       <c r="B3" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136835198</v>
       </c>
       <c r="B4" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136835111</v>
       </c>
       <c r="B5" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22261-2024 artfynd.xlsx
+++ b/artfynd/A 22261-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136835174</v>
       </c>
       <c r="B2" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136835187</v>
       </c>
       <c r="B3" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136835198</v>
       </c>
       <c r="B4" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136835111</v>
       </c>
       <c r="B5" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22261-2024 artfynd.xlsx
+++ b/artfynd/A 22261-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136835174</v>
       </c>
       <c r="B2" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136835187</v>
       </c>
       <c r="B3" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136835198</v>
       </c>
       <c r="B4" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136835111</v>
       </c>
       <c r="B5" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22261-2024 artfynd.xlsx
+++ b/artfynd/A 22261-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136835174</v>
       </c>
       <c r="B2" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136835187</v>
       </c>
       <c r="B3" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136835198</v>
       </c>
       <c r="B4" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136835111</v>
       </c>
       <c r="B5" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22261-2024 artfynd.xlsx
+++ b/artfynd/A 22261-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136835174</v>
       </c>
       <c r="B2" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136835187</v>
       </c>
       <c r="B3" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136835198</v>
       </c>
       <c r="B4" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136835111</v>
       </c>
       <c r="B5" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22261-2024 artfynd.xlsx
+++ b/artfynd/A 22261-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136835174</v>
       </c>
       <c r="B2" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136835187</v>
       </c>
       <c r="B3" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136835198</v>
       </c>
       <c r="B4" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136835111</v>
       </c>
       <c r="B5" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22261-2024 artfynd.xlsx
+++ b/artfynd/A 22261-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136835174</v>
       </c>
       <c r="B2" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136835187</v>
       </c>
       <c r="B3" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136835198</v>
       </c>
       <c r="B4" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136835111</v>
       </c>
       <c r="B5" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22261-2024 artfynd.xlsx
+++ b/artfynd/A 22261-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136835174</v>
       </c>
       <c r="B2" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136835187</v>
       </c>
       <c r="B3" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136835198</v>
       </c>
       <c r="B4" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136835111</v>
       </c>
       <c r="B5" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22261-2024 artfynd.xlsx
+++ b/artfynd/A 22261-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136835174</v>
       </c>
       <c r="B2" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136835187</v>
       </c>
       <c r="B3" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136835198</v>
       </c>
       <c r="B4" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136835111</v>
       </c>
       <c r="B5" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22261-2024 artfynd.xlsx
+++ b/artfynd/A 22261-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136835174</v>
       </c>
       <c r="B2" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136835187</v>
       </c>
       <c r="B3" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136835198</v>
       </c>
       <c r="B4" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136835111</v>
       </c>
       <c r="B5" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22261-2024 artfynd.xlsx
+++ b/artfynd/A 22261-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136835174</v>
       </c>
       <c r="B2" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136835187</v>
       </c>
       <c r="B3" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136835198</v>
       </c>
       <c r="B4" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136835111</v>
       </c>
       <c r="B5" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
